--- a/shop/dist/02-TFSA-vs-RRSP-Contribution-Planner.xlsx
+++ b/shop/dist/02-TFSA-vs-RRSP-Contribution-Planner.xlsx
@@ -750,21 +750,21 @@
     <row r="6">
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>•  TFSA Room — 2009-2026 limits table with your personal room calculated.</t>
+          <t>•  TFSA Room — 2009-2026 limits, counted from age 18 AND Canadian residency.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>•  RRSP Room — 18% rule, dollar cap, pension adjustment and carry-forward.</t>
+          <t>•  RRSP Room — today's room from your CRA notice, and next year's earned room.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>•  TFSA vs RRSP — after-tax comparison with an automatic verdict line.</t>
+          <t>•  TFSA vs RRSP — after-tax comparison capped at your real room, with a plain-English verdict.</t>
         </is>
       </c>
     </row>
@@ -792,21 +792,21 @@
     <row r="13">
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>2.  Open TFSA Room: it builds your room year by year from the date you turned 18.</t>
+          <t>2.  Open TFSA Room: room builds from the later of the year you turned 18 and the year you became a resident.</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>3.  Open RRSP Room: 18% of earned income against the annual cap, plus your carry-forward.</t>
+          <t>3.  Open RRSP Room: today's room comes straight off your CRA notice; next year's is 18% of last year's income.</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>4.  Open TFSA vs RRSP for the side-by-side after-tax answer and a plain-English verdict.</t>
+          <t>4.  Open TFSA vs RRSP for the after-tax answer — capped at the room you actually have.</t>
         </is>
       </c>
     </row>
@@ -878,10 +878,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E29"/>
+  <dimension ref="A1:E33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="56" customWidth="1" min="1" max="1"/>
     <col width="18" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -949,186 +949,210 @@
     <row r="8">
       <c r="A8" s="13" t="inlineStr">
         <is>
-          <t>Planning year</t>
+          <t>Year you became a Canadian resident</t>
         </is>
       </c>
       <c r="B8" s="15" t="n">
-        <v>2026</v>
+        <v>2013</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="13" t="inlineStr">
         <is>
+          <t>Planning year</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n">
+        <v>2026</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="13" t="inlineStr">
+        <is>
           <t>Province / territory</t>
         </is>
       </c>
-      <c r="B9" s="14" t="inlineStr">
+      <c r="B10" s="14" t="inlineStr">
         <is>
           <t>Ontario</t>
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="16" t="inlineStr">
-        <is>
-          <t>TFSA room only starts building the year you turn 18 AND become a Canadian resident.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="11" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="16" t="inlineStr">
+        <is>
+          <t>TFSA room starts in the LATER of the year you turned 18 and the year you became a Canadian resident.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="16" t="inlineStr">
+        <is>
+          <t>If you were born in Canada, put the same year in both boxes.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="11" t="inlineStr">
         <is>
           <t>INCOME &amp; TAX</t>
         </is>
       </c>
-      <c r="B12" s="12" t="n"/>
-      <c r="C12" s="12" t="n"/>
-      <c r="D12" s="12" t="n"/>
-      <c r="E12" s="12" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="13" t="inlineStr">
-        <is>
-          <t>Gross earned income this year</t>
-        </is>
-      </c>
-      <c r="B13" s="17" t="n">
-        <v>78000</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="13" t="inlineStr">
-        <is>
-          <t>Marginal tax rate NOW (combined fed + prov)</t>
-        </is>
-      </c>
-      <c r="B14" s="18" t="n">
-        <v>0.2965</v>
-      </c>
+      <c r="B14" s="12" t="n"/>
+      <c r="C14" s="12" t="n"/>
+      <c r="D14" s="12" t="n"/>
+      <c r="E14" s="12" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="13" t="inlineStr">
         <is>
-          <t>Expected marginal tax rate IN RETIREMENT</t>
-        </is>
-      </c>
-      <c r="B15" s="18" t="n">
-        <v>0.2005</v>
+          <t>Earned income LAST year (employment + net self-employment)</t>
+        </is>
+      </c>
+      <c r="B15" s="17" t="n">
+        <v>78000</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>Employer pension adjustment (from box 52 of your T4)</t>
-        </is>
-      </c>
-      <c r="B16" s="17" t="n">
+          <t>Marginal tax rate NOW (combined fed + prov)</t>
+        </is>
+      </c>
+      <c r="B16" s="18" t="n">
+        <v>0.2965</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="13" t="inlineStr">
+        <is>
+          <t>Expected marginal tax rate IN RETIREMENT</t>
+        </is>
+      </c>
+      <c r="B17" s="18" t="n">
+        <v>0.2005</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="13" t="inlineStr">
+        <is>
+          <t>Pension adjustment last year (box 52 of your T4)</t>
+        </is>
+      </c>
+      <c r="B18" s="17" t="n">
         <v>0</v>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="16" t="inlineStr">
+    <row r="19">
+      <c r="A19" s="16" t="inlineStr">
+        <is>
+          <t>RRSP room is earned on LAST year's income and becomes available THIS year — that is why last year's figure is what belongs here.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="16" t="inlineStr">
         <is>
           <t>Marginal rate = the tax you pay on your NEXT dollar of income, not your average rate.</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="11" t="inlineStr">
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="11" t="inlineStr">
         <is>
           <t>WHAT YOU HAVE ALREADY</t>
         </is>
       </c>
-      <c r="B19" s="12" t="n"/>
-      <c r="C19" s="12" t="n"/>
-      <c r="D19" s="12" t="n"/>
-      <c r="E19" s="12" t="n"/>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>Total TFSA contributions made to date</t>
-        </is>
-      </c>
-      <c r="B20" s="17" t="n">
-        <v>21000</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="13" t="inlineStr">
-        <is>
-          <t>Total TFSA withdrawals in PREVIOUS years</t>
-        </is>
-      </c>
-      <c r="B21" s="17" t="n">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>Unused RRSP room from your latest CRA notice</t>
-        </is>
-      </c>
-      <c r="B22" s="17" t="n">
-        <v>44000</v>
-      </c>
+      <c r="B22" s="12" t="n"/>
+      <c r="C22" s="12" t="n"/>
+      <c r="D22" s="12" t="n"/>
+      <c r="E22" s="12" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="13" t="inlineStr">
         <is>
+          <t>Total TFSA contributions made to date</t>
+        </is>
+      </c>
+      <c r="B23" s="17" t="n">
+        <v>21000</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>Total TFSA withdrawals in PREVIOUS years</t>
+        </is>
+      </c>
+      <c r="B24" s="17" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>RRSP deduction limit for this year (from your CRA notice)</t>
+        </is>
+      </c>
+      <c r="B25" s="17" t="n">
+        <v>44000</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
           <t>RRSP contributions already made this year</t>
         </is>
       </c>
-      <c r="B23" s="17" t="n">
+      <c r="B26" s="17" t="n">
         <v>3000</v>
       </c>
     </row>
-    <row r="24">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>Your CRA My Account notice of assessment is the authoritative source for both room figures.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="11" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="16" t="inlineStr">
+        <is>
+          <t>Your CRA My Account notice of assessment is the authoritative source. The RRSP deduction limit it shows ALREADY includes your carry-forward — do not add anything to it.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="11" t="inlineStr">
         <is>
           <t>PLANNING ASSUMPTIONS</t>
         </is>
       </c>
-      <c r="B26" s="12" t="n"/>
-      <c r="C26" s="12" t="n"/>
-      <c r="D26" s="12" t="n"/>
-      <c r="E26" s="12" t="n"/>
-    </row>
-    <row r="27">
-      <c r="A27" s="13" t="inlineStr">
+      <c r="B30" s="12" t="n"/>
+      <c r="C30" s="12" t="n"/>
+      <c r="D30" s="12" t="n"/>
+      <c r="E30" s="12" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>Amount you can save per year</t>
         </is>
       </c>
-      <c r="B27" s="17" t="n">
+      <c r="B31" s="17" t="n">
         <v>12000</v>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="13" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="13" t="inlineStr">
         <is>
           <t>Expected annual investment return</t>
         </is>
       </c>
-      <c r="B28" s="18" t="n">
+      <c r="B32" s="18" t="n">
         <v>0.06</v>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="13" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="13" t="inlineStr">
         <is>
           <t>Years until you draw the money</t>
         </is>
       </c>
-      <c r="B29" s="15" t="n">
+      <c r="B33" s="15" t="n">
         <v>25</v>
       </c>
     </row>
@@ -1144,7 +1168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D31"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1166,7 +1190,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Year-by-year contribution room from 2009 to today.</t>
+          <t>Year-by-year room, counted from the later of age 18 and Canadian residency.</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1203,7 +1227,7 @@
         <v>5000</v>
       </c>
       <c r="C5" s="22">
-        <f>IF(AND(A5&gt;='Your Numbers'!$B$7,A5&lt;='Your Numbers'!$B$8),"Yes","No")</f>
+        <f>IF(AND(A5&gt;=MAX('Your Numbers'!$B$7,'Your Numbers'!$B$8),A5&lt;='Your Numbers'!$B$9),"Yes","No")</f>
         <v/>
       </c>
       <c r="D5" s="23">
@@ -1219,7 +1243,7 @@
         <v>5000</v>
       </c>
       <c r="C6" s="22">
-        <f>IF(AND(A6&gt;='Your Numbers'!$B$7,A6&lt;='Your Numbers'!$B$8),"Yes","No")</f>
+        <f>IF(AND(A6&gt;=MAX('Your Numbers'!$B$7,'Your Numbers'!$B$8),A6&lt;='Your Numbers'!$B$9),"Yes","No")</f>
         <v/>
       </c>
       <c r="D6" s="23">
@@ -1235,7 +1259,7 @@
         <v>5000</v>
       </c>
       <c r="C7" s="22">
-        <f>IF(AND(A7&gt;='Your Numbers'!$B$7,A7&lt;='Your Numbers'!$B$8),"Yes","No")</f>
+        <f>IF(AND(A7&gt;=MAX('Your Numbers'!$B$7,'Your Numbers'!$B$8),A7&lt;='Your Numbers'!$B$9),"Yes","No")</f>
         <v/>
       </c>
       <c r="D7" s="23">
@@ -1251,7 +1275,7 @@
         <v>5000</v>
       </c>
       <c r="C8" s="22">
-        <f>IF(AND(A8&gt;='Your Numbers'!$B$7,A8&lt;='Your Numbers'!$B$8),"Yes","No")</f>
+        <f>IF(AND(A8&gt;=MAX('Your Numbers'!$B$7,'Your Numbers'!$B$8),A8&lt;='Your Numbers'!$B$9),"Yes","No")</f>
         <v/>
       </c>
       <c r="D8" s="23">
@@ -1267,7 +1291,7 @@
         <v>5500</v>
       </c>
       <c r="C9" s="22">
-        <f>IF(AND(A9&gt;='Your Numbers'!$B$7,A9&lt;='Your Numbers'!$B$8),"Yes","No")</f>
+        <f>IF(AND(A9&gt;=MAX('Your Numbers'!$B$7,'Your Numbers'!$B$8),A9&lt;='Your Numbers'!$B$9),"Yes","No")</f>
         <v/>
       </c>
       <c r="D9" s="23">
@@ -1283,7 +1307,7 @@
         <v>5500</v>
       </c>
       <c r="C10" s="22">
-        <f>IF(AND(A10&gt;='Your Numbers'!$B$7,A10&lt;='Your Numbers'!$B$8),"Yes","No")</f>
+        <f>IF(AND(A10&gt;=MAX('Your Numbers'!$B$7,'Your Numbers'!$B$8),A10&lt;='Your Numbers'!$B$9),"Yes","No")</f>
         <v/>
       </c>
       <c r="D10" s="23">
@@ -1299,7 +1323,7 @@
         <v>10000</v>
       </c>
       <c r="C11" s="22">
-        <f>IF(AND(A11&gt;='Your Numbers'!$B$7,A11&lt;='Your Numbers'!$B$8),"Yes","No")</f>
+        <f>IF(AND(A11&gt;=MAX('Your Numbers'!$B$7,'Your Numbers'!$B$8),A11&lt;='Your Numbers'!$B$9),"Yes","No")</f>
         <v/>
       </c>
       <c r="D11" s="23">
@@ -1315,7 +1339,7 @@
         <v>5500</v>
       </c>
       <c r="C12" s="22">
-        <f>IF(AND(A12&gt;='Your Numbers'!$B$7,A12&lt;='Your Numbers'!$B$8),"Yes","No")</f>
+        <f>IF(AND(A12&gt;=MAX('Your Numbers'!$B$7,'Your Numbers'!$B$8),A12&lt;='Your Numbers'!$B$9),"Yes","No")</f>
         <v/>
       </c>
       <c r="D12" s="23">
@@ -1331,7 +1355,7 @@
         <v>5500</v>
       </c>
       <c r="C13" s="22">
-        <f>IF(AND(A13&gt;='Your Numbers'!$B$7,A13&lt;='Your Numbers'!$B$8),"Yes","No")</f>
+        <f>IF(AND(A13&gt;=MAX('Your Numbers'!$B$7,'Your Numbers'!$B$8),A13&lt;='Your Numbers'!$B$9),"Yes","No")</f>
         <v/>
       </c>
       <c r="D13" s="23">
@@ -1347,7 +1371,7 @@
         <v>5500</v>
       </c>
       <c r="C14" s="22">
-        <f>IF(AND(A14&gt;='Your Numbers'!$B$7,A14&lt;='Your Numbers'!$B$8),"Yes","No")</f>
+        <f>IF(AND(A14&gt;=MAX('Your Numbers'!$B$7,'Your Numbers'!$B$8),A14&lt;='Your Numbers'!$B$9),"Yes","No")</f>
         <v/>
       </c>
       <c r="D14" s="23">
@@ -1363,7 +1387,7 @@
         <v>6000</v>
       </c>
       <c r="C15" s="22">
-        <f>IF(AND(A15&gt;='Your Numbers'!$B$7,A15&lt;='Your Numbers'!$B$8),"Yes","No")</f>
+        <f>IF(AND(A15&gt;=MAX('Your Numbers'!$B$7,'Your Numbers'!$B$8),A15&lt;='Your Numbers'!$B$9),"Yes","No")</f>
         <v/>
       </c>
       <c r="D15" s="23">
@@ -1379,7 +1403,7 @@
         <v>6000</v>
       </c>
       <c r="C16" s="22">
-        <f>IF(AND(A16&gt;='Your Numbers'!$B$7,A16&lt;='Your Numbers'!$B$8),"Yes","No")</f>
+        <f>IF(AND(A16&gt;=MAX('Your Numbers'!$B$7,'Your Numbers'!$B$8),A16&lt;='Your Numbers'!$B$9),"Yes","No")</f>
         <v/>
       </c>
       <c r="D16" s="23">
@@ -1395,7 +1419,7 @@
         <v>6000</v>
       </c>
       <c r="C17" s="22">
-        <f>IF(AND(A17&gt;='Your Numbers'!$B$7,A17&lt;='Your Numbers'!$B$8),"Yes","No")</f>
+        <f>IF(AND(A17&gt;=MAX('Your Numbers'!$B$7,'Your Numbers'!$B$8),A17&lt;='Your Numbers'!$B$9),"Yes","No")</f>
         <v/>
       </c>
       <c r="D17" s="23">
@@ -1411,7 +1435,7 @@
         <v>6000</v>
       </c>
       <c r="C18" s="22">
-        <f>IF(AND(A18&gt;='Your Numbers'!$B$7,A18&lt;='Your Numbers'!$B$8),"Yes","No")</f>
+        <f>IF(AND(A18&gt;=MAX('Your Numbers'!$B$7,'Your Numbers'!$B$8),A18&lt;='Your Numbers'!$B$9),"Yes","No")</f>
         <v/>
       </c>
       <c r="D18" s="23">
@@ -1427,7 +1451,7 @@
         <v>6500</v>
       </c>
       <c r="C19" s="22">
-        <f>IF(AND(A19&gt;='Your Numbers'!$B$7,A19&lt;='Your Numbers'!$B$8),"Yes","No")</f>
+        <f>IF(AND(A19&gt;=MAX('Your Numbers'!$B$7,'Your Numbers'!$B$8),A19&lt;='Your Numbers'!$B$9),"Yes","No")</f>
         <v/>
       </c>
       <c r="D19" s="23">
@@ -1443,7 +1467,7 @@
         <v>7000</v>
       </c>
       <c r="C20" s="22">
-        <f>IF(AND(A20&gt;='Your Numbers'!$B$7,A20&lt;='Your Numbers'!$B$8),"Yes","No")</f>
+        <f>IF(AND(A20&gt;=MAX('Your Numbers'!$B$7,'Your Numbers'!$B$8),A20&lt;='Your Numbers'!$B$9),"Yes","No")</f>
         <v/>
       </c>
       <c r="D20" s="23">
@@ -1459,7 +1483,7 @@
         <v>7000</v>
       </c>
       <c r="C21" s="22">
-        <f>IF(AND(A21&gt;='Your Numbers'!$B$7,A21&lt;='Your Numbers'!$B$8),"Yes","No")</f>
+        <f>IF(AND(A21&gt;=MAX('Your Numbers'!$B$7,'Your Numbers'!$B$8),A21&lt;='Your Numbers'!$B$9),"Yes","No")</f>
         <v/>
       </c>
       <c r="D21" s="23">
@@ -1475,7 +1499,7 @@
         <v>7000</v>
       </c>
       <c r="C22" s="22">
-        <f>IF(AND(A22&gt;='Your Numbers'!$B$7,A22&lt;='Your Numbers'!$B$8),"Yes","No")</f>
+        <f>IF(AND(A22&gt;=MAX('Your Numbers'!$B$7,'Your Numbers'!$B$8),A22&lt;='Your Numbers'!$B$9),"Yes","No")</f>
         <v/>
       </c>
       <c r="D22" s="23">
@@ -1501,7 +1525,7 @@
         </is>
       </c>
       <c r="B25" s="23">
-        <f>'Your Numbers'!$B$20</f>
+        <f>'Your Numbers'!$B$23</f>
         <v/>
       </c>
     </row>
@@ -1512,7 +1536,7 @@
         </is>
       </c>
       <c r="B26" s="23">
-        <f>'Your Numbers'!$B$21</f>
+        <f>'Your Numbers'!$B$24</f>
         <v/>
       </c>
     </row>
@@ -1523,7 +1547,7 @@
         </is>
       </c>
       <c r="B27" s="24">
-        <f>B24-B25+B26</f>
+        <f>MAX(0,B24-B25+B26)</f>
         <v/>
       </c>
     </row>
@@ -1545,6 +1569,13 @@
       <c r="A31" s="16" t="inlineStr">
         <is>
           <t>Over-contributing costs 1% of the excess per month. Check CRA My Account if you are close to the line.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>Newcomers: room does NOT build for years you were not a Canadian resident, even if you were over 18.</t>
         </is>
       </c>
     </row>
@@ -1560,10 +1591,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D25"/>
+  <dimension ref="A1:D32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="54" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
@@ -1580,7 +1611,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>18% of earned income, capped at the annual dollar limit.</t>
+          <t>What you can contribute today, and what next year's room will be.</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1663,113 +1694,156 @@
         <v>33810</v>
       </c>
     </row>
-    <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="11" t="inlineStr">
-        <is>
-          <t>THIS YEAR'S ROOM</t>
-        </is>
-      </c>
-      <c r="B14" s="12" t="n"/>
-      <c r="C14" s="12" t="n"/>
-      <c r="D14" s="12" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="13" t="inlineStr">
-        <is>
-          <t>18% of earned income</t>
-        </is>
-      </c>
-      <c r="B15" s="23">
-        <f>0.18*'Your Numbers'!$B$13</f>
-        <v/>
-      </c>
+    <row r="13">
+      <c r="A13" s="20" t="n">
+        <v>2027</v>
+      </c>
+      <c r="B13" s="21" t="n">
+        <v>35130</v>
+      </c>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="11" t="inlineStr">
+        <is>
+          <t>ROOM AVAILABLE TO YOU TODAY</t>
+        </is>
+      </c>
+      <c r="B15" s="12" t="n"/>
+      <c r="C15" s="12" t="n"/>
+      <c r="D15" s="12" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="13" t="inlineStr">
         <is>
-          <t>Dollar limit for the planning year</t>
+          <t>RRSP deduction limit for this year (from your CRA notice)</t>
         </is>
       </c>
       <c r="B16" s="23">
-        <f>IFERROR(VLOOKUP('Your Numbers'!$B$8,A5:B12,2,FALSE),MAX(B5:B12))</f>
+        <f>'Your Numbers'!$B$25</f>
         <v/>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="13" t="inlineStr">
         <is>
-          <t>New room earned (lesser of the two)</t>
+          <t>Less: contributions already made this year</t>
         </is>
       </c>
       <c r="B17" s="23">
-        <f>MIN(B15,B16)</f>
+        <f>'Your Numbers'!$B$26</f>
         <v/>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>Less: pension adjustment</t>
-        </is>
-      </c>
-      <c r="B18" s="23">
-        <f>'Your Numbers'!$B$16</f>
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>ROOM AVAILABLE TODAY</t>
+        </is>
+      </c>
+      <c r="B18" s="24">
+        <f>MAX(0,B16-B17)</f>
         <v/>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="13" t="inlineStr">
         <is>
-          <t>Plus: unused room carried forward</t>
-        </is>
-      </c>
-      <c r="B19" s="23">
-        <f>'Your Numbers'!$B$22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="13" t="inlineStr">
-        <is>
-          <t>Less: contributions already made</t>
-        </is>
-      </c>
-      <c r="B20" s="23">
-        <f>'Your Numbers'!$B$23</f>
+          <t>Tax refund if you contribute it all</t>
+        </is>
+      </c>
+      <c r="B19" s="24">
+        <f>B18*'Your Numbers'!$B$16</f>
         <v/>
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="4" t="inlineStr">
-        <is>
-          <t>ROOM AVAILABLE TODAY</t>
-        </is>
-      </c>
-      <c r="B21" s="24">
-        <f>B17-B18+B19-B20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>Tax refund if you contribute it all</t>
-        </is>
-      </c>
-      <c r="B22" s="24">
-        <f>MAX(0,B21)*'Your Numbers'!$B$14</f>
-        <v/>
-      </c>
+      <c r="A21" s="16" t="inlineStr">
+        <is>
+          <t>The deduction limit on your notice of assessment ALREADY includes every unused dollar carried forward. Adding this year's new room to it would double-count.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="11" t="inlineStr">
+        <is>
+          <t>ROOM YOU WILL EARN FOR NEXT YEAR</t>
+        </is>
+      </c>
+      <c r="B23" s="12" t="n"/>
+      <c r="C23" s="12" t="n"/>
+      <c r="D23" s="12" t="n"/>
     </row>
     <row r="24">
-      <c r="A24" s="16" t="inlineStr">
-        <is>
-          <t>Dollar limits are as published by CRA; the 2026 figure is indexed — verify before filing.</t>
-        </is>
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>18% of last year's earned income</t>
+        </is>
+      </c>
+      <c r="B24" s="23">
+        <f>0.18*'Your Numbers'!$B$15</f>
+        <v/>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="16" t="inlineStr">
+      <c r="A25" s="13" t="inlineStr">
+        <is>
+          <t>Dollar limit for next year</t>
+        </is>
+      </c>
+      <c r="B25" s="23">
+        <f>IFERROR(VLOOKUP('Your Numbers'!$B$9+1,A5:B13,2,FALSE),MAX(B5:B13))</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="13" t="inlineStr">
+        <is>
+          <t>New room earned (lesser of the two)</t>
+        </is>
+      </c>
+      <c r="B26" s="23">
+        <f>MIN(B24,B25)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="13" t="inlineStr">
+        <is>
+          <t>Less: pension adjustment</t>
+        </is>
+      </c>
+      <c r="B27" s="23">
+        <f>'Your Numbers'!$B$18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>ROOM ADDED FOR NEXT YEAR</t>
+        </is>
+      </c>
+      <c r="B28" s="24">
+        <f>MAX(0,B26-B27)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="16" t="inlineStr">
+        <is>
+          <t>Contributions earn room on the PREVIOUS year's income: 18% of what you earned last year is what became available this year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="16" t="inlineStr">
+        <is>
+          <t>Dollar limits are as published by CRA; later years are indexed — verify before filing.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="16" t="inlineStr">
         <is>
           <t>You have a $2,000 lifetime over-contribution cushion, but it is not deductible. Do not lean on it.</t>
         </is>
@@ -1787,7 +1861,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1811,7 +1885,7 @@
     <row r="2" ht="18" customHeight="1">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Same dollars, both accounts, side by side after tax.</t>
+          <t>Same dollars, both accounts, side by side after tax — capped at the room you actually have.</t>
         </is>
       </c>
       <c r="B2" s="2" t="n"/>
@@ -1853,89 +1927,88 @@
     <row r="6">
       <c r="A6" s="25" t="inlineStr">
         <is>
-          <t>Amount contributed</t>
+          <t>Amount you want to save</t>
         </is>
       </c>
       <c r="B6" s="23">
-        <f>'Your Numbers'!$B$27</f>
+        <f>'Your Numbers'!$B$31</f>
         <v/>
       </c>
       <c r="C6" s="23">
-        <f>'Your Numbers'!$B$27</f>
+        <f>'Your Numbers'!$B$31</f>
         <v/>
       </c>
       <c r="D6" s="16" t="inlineStr">
         <is>
-          <t>The same out-of-pocket dollars either way.</t>
+          <t>What you told the Your Numbers tab you can put away.</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="25" t="inlineStr">
         <is>
-          <t>Immediate tax refund</t>
-        </is>
-      </c>
-      <c r="B7" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>Room available in this account</t>
+        </is>
+      </c>
+      <c r="B7" s="23">
+        <f>'TFSA Room'!$B$27</f>
+        <v/>
       </c>
       <c r="C7" s="23">
-        <f>'Your Numbers'!$B$27*'Your Numbers'!$B$14</f>
+        <f>'RRSP Room'!$B$18</f>
         <v/>
       </c>
       <c r="D7" s="16" t="inlineStr">
         <is>
-          <t>RRSP contributions are deductible; TFSA contributions are not.</t>
+          <t>Pulled from the two room tabs. This is the ceiling.</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="25" t="inlineStr">
         <is>
-          <t>Refund reinvested at the same return</t>
-        </is>
-      </c>
-      <c r="B8" s="23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
+          <t>Amount actually contributed</t>
+        </is>
+      </c>
+      <c r="B8" s="23">
+        <f>MIN(B6,B7)</f>
+        <v/>
       </c>
       <c r="C8" s="23">
-        <f>C7*(1+'Your Numbers'!$B$28)^'Your Numbers'!$B$29</f>
+        <f>MIN(C6,C7)</f>
         <v/>
       </c>
       <c r="D8" s="16" t="inlineStr">
         <is>
-          <t>Only counts if you actually invest the refund.</t>
+          <t>Capped at your room — the planner will not model an over-contribution.</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="25" t="inlineStr">
         <is>
-          <t>Value at the end of the horizon</t>
-        </is>
-      </c>
-      <c r="B9" s="23">
-        <f>B6*(1+'Your Numbers'!$B$28)^'Your Numbers'!$B$29</f>
-        <v/>
+          <t>Immediate tax refund</t>
+        </is>
+      </c>
+      <c r="B9" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="C9" s="23">
-        <f>C6*(1+'Your Numbers'!$B$28)^'Your Numbers'!$B$29</f>
+        <f>C8*'Your Numbers'!$B$16</f>
         <v/>
       </c>
       <c r="D9" s="16" t="inlineStr">
         <is>
-          <t>Growth before any tax on withdrawal.</t>
+          <t>RRSP contributions are deductible; TFSA contributions are not.</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="25" t="inlineStr">
         <is>
-          <t>Tax on withdrawal</t>
+          <t>Refund reinvested at the same return</t>
         </is>
       </c>
       <c r="B10" s="23" t="inlineStr">
@@ -1944,120 +2017,172 @@
         </is>
       </c>
       <c r="C10" s="23">
-        <f>-C9*'Your Numbers'!$B$15</f>
+        <f>C9*(1+'Your Numbers'!$B$32)^'Your Numbers'!$B$33</f>
         <v/>
       </c>
       <c r="D10" s="16" t="inlineStr">
         <is>
-          <t>RRSP/RRIF withdrawals are fully taxable as income.</t>
+          <t>Only counts if you actually invest the refund.</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="25" t="inlineStr">
         <is>
+          <t>Value at the end of the horizon</t>
+        </is>
+      </c>
+      <c r="B11" s="23">
+        <f>B8*(1+'Your Numbers'!$B$32)^'Your Numbers'!$B$33</f>
+        <v/>
+      </c>
+      <c r="C11" s="23">
+        <f>C8*(1+'Your Numbers'!$B$32)^'Your Numbers'!$B$33</f>
+        <v/>
+      </c>
+      <c r="D11" s="16" t="inlineStr">
+        <is>
+          <t>Growth before any tax on withdrawal.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="25" t="inlineStr">
+        <is>
+          <t>Tax on withdrawal</t>
+        </is>
+      </c>
+      <c r="B12" s="23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="C12" s="23">
+        <f>-C11*'Your Numbers'!$B$17</f>
+        <v/>
+      </c>
+      <c r="D12" s="16" t="inlineStr">
+        <is>
+          <t>RRSP/RRIF withdrawals are fully taxable as income.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="25" t="inlineStr">
+        <is>
           <t>Refund pot after tax (non-registered, simplified)</t>
         </is>
       </c>
-      <c r="B11" s="23" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="C11" s="23">
-        <f>C8*(1-'Your Numbers'!$B$15*0.5)</f>
-        <v/>
-      </c>
-      <c r="D11" s="16" t="inlineStr">
+      <c r="C13" s="23">
+        <f>C10*(1-'Your Numbers'!$B$17*0.5)</f>
+        <v/>
+      </c>
+      <c r="D13" s="16" t="inlineStr">
         <is>
           <t>Assumes the refund grows in a taxable account.</t>
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="13" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="13" t="inlineStr">
         <is>
           <t>AFTER-TAX VALUE</t>
         </is>
       </c>
-      <c r="B12" s="24">
-        <f>B9</f>
-        <v/>
-      </c>
-      <c r="C12" s="24">
-        <f>C9+C10+C11</f>
-        <v/>
-      </c>
-      <c r="D12" s="16" t="inlineStr">
+      <c r="B14" s="24">
+        <f>B11</f>
+        <v/>
+      </c>
+      <c r="C14" s="24">
+        <f>C11+C12+C13</f>
+        <v/>
+      </c>
+      <c r="D14" s="16" t="inlineStr">
         <is>
           <t>The number that actually matters.</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="4" t="inlineStr">
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
         <is>
           <t>WHICH ONE WINS FOR YOU</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="32" customHeight="1">
-      <c r="A15" s="26">
-        <f>IF('Your Numbers'!$B$14&gt;'Your Numbers'!$B$15,"RRSP first — you deduct at a higher rate than you will pay on withdrawal.",IF('Your Numbers'!$B$14&lt;'Your Numbers'!$B$15,"TFSA first — you would deduct at a low rate and pay tax at a higher one later.","Close call — your rate now equals your expected rate later, so use the TFSA for flexibility."))</f>
-        <v/>
-      </c>
-      <c r="B15" s="27" t="n"/>
-      <c r="C15" s="27" t="n"/>
-      <c r="D15" s="28" t="n"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="11" t="inlineStr">
+    <row r="17" ht="38" customHeight="1">
+      <c r="A17" s="26">
+        <f>IF(AND('TFSA Room'!$B$27&lt;=0,'RRSP Room'!$B$18&lt;=0),"You have no room left in either account this year. Anything more goes to a non-registered account, or waits for January.",IF('RRSP Room'!$B$18&lt;=0,"TFSA — you have no RRSP room left this year.",IF('TFSA Room'!$B$27&lt;=0,"RRSP — you have no TFSA room left this year.",IF('Your Numbers'!$B$16&gt;'Your Numbers'!$B$17,"RRSP first — you deduct at a higher rate than you will pay on withdrawal."&amp;IF('RRSP Room'!$B$18&lt;'Your Numbers'!$B$31," Your RRSP room runs out before your savings do, so put the remainder in your TFSA.",""),IF('Your Numbers'!$B$16&lt;'Your Numbers'!$B$17,"TFSA first — you would deduct at a low rate now and pay tax at a higher one later."&amp;IF('TFSA Room'!$B$27&lt;'Your Numbers'!$B$31," Your TFSA room runs out before your savings do, so put the remainder in your RRSP.",""),"Close call — your rate now equals your expected rate later, so use the TFSA for its flexibility.")))))</f>
+        <v/>
+      </c>
+      <c r="B17" s="27" t="n"/>
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="28" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="11" t="inlineStr">
         <is>
           <t>YOUR ROOM, PULLED FROM THE OTHER TABS</t>
         </is>
       </c>
-      <c r="B17" s="12" t="n"/>
-      <c r="C17" s="12" t="n"/>
-      <c r="D17" s="12" t="n"/>
-      <c r="E17" s="12" t="n"/>
-      <c r="F17" s="12" t="n"/>
-    </row>
-    <row r="18">
-      <c r="A18" s="13" t="inlineStr">
-        <is>
-          <t>TFSA room available</t>
-        </is>
-      </c>
-      <c r="B18" s="24">
-        <f>'TFSA Room'!$B$27</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="13" t="inlineStr">
-        <is>
-          <t>RRSP room available</t>
-        </is>
-      </c>
-      <c r="B19" s="24">
-        <f>'RRSP Room'!$B$21</f>
-        <v/>
-      </c>
+      <c r="B19" s="12" t="n"/>
+      <c r="C19" s="12" t="n"/>
+      <c r="D19" s="12" t="n"/>
+      <c r="E19" s="12" t="n"/>
+      <c r="F19" s="12" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="13" t="inlineStr">
         <is>
+          <t>TFSA room available</t>
+        </is>
+      </c>
+      <c r="B20" s="24">
+        <f>'TFSA Room'!$B$27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="13" t="inlineStr">
+        <is>
+          <t>RRSP room available</t>
+        </is>
+      </c>
+      <c r="B21" s="24">
+        <f>'RRSP Room'!$B$18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="13" t="inlineStr">
+        <is>
           <t>Total room available</t>
         </is>
       </c>
-      <c r="B20" s="24">
-        <f>B18+B19</f>
+      <c r="B22" s="24">
+        <f>B20+B21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>Savings with nowhere registered to go</t>
+        </is>
+      </c>
+      <c r="B23" s="24">
+        <f>MAX(0,'Your Numbers'!$B$31-B22)</f>
         <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A15:D15"/>
+    <mergeCell ref="A17:D17"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2134,7 +2259,7 @@
         <v>1</v>
       </c>
       <c r="B5" s="23">
-        <f>IF(A5&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A5&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C5" s="23">
@@ -2142,7 +2267,7 @@
         <v/>
       </c>
       <c r="D5" s="23">
-        <f>(0+B5)*'Your Numbers'!$B$28</f>
+        <f>(0+B5)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E5" s="24">
@@ -2155,7 +2280,7 @@
         <v>2</v>
       </c>
       <c r="B6" s="23">
-        <f>IF(A6&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A6&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C6" s="23">
@@ -2163,7 +2288,7 @@
         <v/>
       </c>
       <c r="D6" s="23">
-        <f>(E5+B6)*'Your Numbers'!$B$28</f>
+        <f>(E5+B6)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E6" s="24">
@@ -2176,7 +2301,7 @@
         <v>3</v>
       </c>
       <c r="B7" s="23">
-        <f>IF(A7&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A7&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C7" s="23">
@@ -2184,7 +2309,7 @@
         <v/>
       </c>
       <c r="D7" s="23">
-        <f>(E6+B7)*'Your Numbers'!$B$28</f>
+        <f>(E6+B7)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E7" s="24">
@@ -2197,7 +2322,7 @@
         <v>4</v>
       </c>
       <c r="B8" s="23">
-        <f>IF(A8&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A8&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C8" s="23">
@@ -2205,7 +2330,7 @@
         <v/>
       </c>
       <c r="D8" s="23">
-        <f>(E7+B8)*'Your Numbers'!$B$28</f>
+        <f>(E7+B8)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E8" s="24">
@@ -2218,7 +2343,7 @@
         <v>5</v>
       </c>
       <c r="B9" s="23">
-        <f>IF(A9&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A9&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C9" s="23">
@@ -2226,7 +2351,7 @@
         <v/>
       </c>
       <c r="D9" s="23">
-        <f>(E8+B9)*'Your Numbers'!$B$28</f>
+        <f>(E8+B9)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E9" s="24">
@@ -2239,7 +2364,7 @@
         <v>6</v>
       </c>
       <c r="B10" s="23">
-        <f>IF(A10&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A10&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C10" s="23">
@@ -2247,7 +2372,7 @@
         <v/>
       </c>
       <c r="D10" s="23">
-        <f>(E9+B10)*'Your Numbers'!$B$28</f>
+        <f>(E9+B10)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E10" s="24">
@@ -2260,7 +2385,7 @@
         <v>7</v>
       </c>
       <c r="B11" s="23">
-        <f>IF(A11&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A11&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C11" s="23">
@@ -2268,7 +2393,7 @@
         <v/>
       </c>
       <c r="D11" s="23">
-        <f>(E10+B11)*'Your Numbers'!$B$28</f>
+        <f>(E10+B11)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E11" s="24">
@@ -2281,7 +2406,7 @@
         <v>8</v>
       </c>
       <c r="B12" s="23">
-        <f>IF(A12&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A12&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C12" s="23">
@@ -2289,7 +2414,7 @@
         <v/>
       </c>
       <c r="D12" s="23">
-        <f>(E11+B12)*'Your Numbers'!$B$28</f>
+        <f>(E11+B12)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E12" s="24">
@@ -2302,7 +2427,7 @@
         <v>9</v>
       </c>
       <c r="B13" s="23">
-        <f>IF(A13&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A13&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C13" s="23">
@@ -2310,7 +2435,7 @@
         <v/>
       </c>
       <c r="D13" s="23">
-        <f>(E12+B13)*'Your Numbers'!$B$28</f>
+        <f>(E12+B13)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E13" s="24">
@@ -2323,7 +2448,7 @@
         <v>10</v>
       </c>
       <c r="B14" s="23">
-        <f>IF(A14&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A14&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C14" s="23">
@@ -2331,7 +2456,7 @@
         <v/>
       </c>
       <c r="D14" s="23">
-        <f>(E13+B14)*'Your Numbers'!$B$28</f>
+        <f>(E13+B14)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E14" s="24">
@@ -2344,7 +2469,7 @@
         <v>11</v>
       </c>
       <c r="B15" s="23">
-        <f>IF(A15&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A15&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C15" s="23">
@@ -2352,7 +2477,7 @@
         <v/>
       </c>
       <c r="D15" s="23">
-        <f>(E14+B15)*'Your Numbers'!$B$28</f>
+        <f>(E14+B15)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E15" s="24">
@@ -2365,7 +2490,7 @@
         <v>12</v>
       </c>
       <c r="B16" s="23">
-        <f>IF(A16&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A16&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C16" s="23">
@@ -2373,7 +2498,7 @@
         <v/>
       </c>
       <c r="D16" s="23">
-        <f>(E15+B16)*'Your Numbers'!$B$28</f>
+        <f>(E15+B16)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E16" s="24">
@@ -2386,7 +2511,7 @@
         <v>13</v>
       </c>
       <c r="B17" s="23">
-        <f>IF(A17&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A17&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C17" s="23">
@@ -2394,7 +2519,7 @@
         <v/>
       </c>
       <c r="D17" s="23">
-        <f>(E16+B17)*'Your Numbers'!$B$28</f>
+        <f>(E16+B17)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E17" s="24">
@@ -2407,7 +2532,7 @@
         <v>14</v>
       </c>
       <c r="B18" s="23">
-        <f>IF(A18&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A18&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C18" s="23">
@@ -2415,7 +2540,7 @@
         <v/>
       </c>
       <c r="D18" s="23">
-        <f>(E17+B18)*'Your Numbers'!$B$28</f>
+        <f>(E17+B18)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E18" s="24">
@@ -2428,7 +2553,7 @@
         <v>15</v>
       </c>
       <c r="B19" s="23">
-        <f>IF(A19&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A19&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C19" s="23">
@@ -2436,7 +2561,7 @@
         <v/>
       </c>
       <c r="D19" s="23">
-        <f>(E18+B19)*'Your Numbers'!$B$28</f>
+        <f>(E18+B19)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E19" s="24">
@@ -2449,7 +2574,7 @@
         <v>16</v>
       </c>
       <c r="B20" s="23">
-        <f>IF(A20&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A20&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C20" s="23">
@@ -2457,7 +2582,7 @@
         <v/>
       </c>
       <c r="D20" s="23">
-        <f>(E19+B20)*'Your Numbers'!$B$28</f>
+        <f>(E19+B20)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E20" s="24">
@@ -2470,7 +2595,7 @@
         <v>17</v>
       </c>
       <c r="B21" s="23">
-        <f>IF(A21&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A21&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C21" s="23">
@@ -2478,7 +2603,7 @@
         <v/>
       </c>
       <c r="D21" s="23">
-        <f>(E20+B21)*'Your Numbers'!$B$28</f>
+        <f>(E20+B21)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E21" s="24">
@@ -2491,7 +2616,7 @@
         <v>18</v>
       </c>
       <c r="B22" s="23">
-        <f>IF(A22&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A22&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C22" s="23">
@@ -2499,7 +2624,7 @@
         <v/>
       </c>
       <c r="D22" s="23">
-        <f>(E21+B22)*'Your Numbers'!$B$28</f>
+        <f>(E21+B22)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E22" s="24">
@@ -2512,7 +2637,7 @@
         <v>19</v>
       </c>
       <c r="B23" s="23">
-        <f>IF(A23&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A23&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C23" s="23">
@@ -2520,7 +2645,7 @@
         <v/>
       </c>
       <c r="D23" s="23">
-        <f>(E22+B23)*'Your Numbers'!$B$28</f>
+        <f>(E22+B23)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E23" s="24">
@@ -2533,7 +2658,7 @@
         <v>20</v>
       </c>
       <c r="B24" s="23">
-        <f>IF(A24&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A24&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C24" s="23">
@@ -2541,7 +2666,7 @@
         <v/>
       </c>
       <c r="D24" s="23">
-        <f>(E23+B24)*'Your Numbers'!$B$28</f>
+        <f>(E23+B24)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E24" s="24">
@@ -2554,7 +2679,7 @@
         <v>21</v>
       </c>
       <c r="B25" s="23">
-        <f>IF(A25&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A25&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C25" s="23">
@@ -2562,7 +2687,7 @@
         <v/>
       </c>
       <c r="D25" s="23">
-        <f>(E24+B25)*'Your Numbers'!$B$28</f>
+        <f>(E24+B25)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E25" s="24">
@@ -2575,7 +2700,7 @@
         <v>22</v>
       </c>
       <c r="B26" s="23">
-        <f>IF(A26&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A26&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C26" s="23">
@@ -2583,7 +2708,7 @@
         <v/>
       </c>
       <c r="D26" s="23">
-        <f>(E25+B26)*'Your Numbers'!$B$28</f>
+        <f>(E25+B26)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E26" s="24">
@@ -2596,7 +2721,7 @@
         <v>23</v>
       </c>
       <c r="B27" s="23">
-        <f>IF(A27&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A27&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C27" s="23">
@@ -2604,7 +2729,7 @@
         <v/>
       </c>
       <c r="D27" s="23">
-        <f>(E26+B27)*'Your Numbers'!$B$28</f>
+        <f>(E26+B27)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E27" s="24">
@@ -2617,7 +2742,7 @@
         <v>24</v>
       </c>
       <c r="B28" s="23">
-        <f>IF(A28&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A28&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C28" s="23">
@@ -2625,7 +2750,7 @@
         <v/>
       </c>
       <c r="D28" s="23">
-        <f>(E27+B28)*'Your Numbers'!$B$28</f>
+        <f>(E27+B28)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E28" s="24">
@@ -2638,7 +2763,7 @@
         <v>25</v>
       </c>
       <c r="B29" s="23">
-        <f>IF(A29&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A29&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C29" s="23">
@@ -2646,7 +2771,7 @@
         <v/>
       </c>
       <c r="D29" s="23">
-        <f>(E28+B29)*'Your Numbers'!$B$28</f>
+        <f>(E28+B29)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E29" s="24">
@@ -2659,7 +2784,7 @@
         <v>26</v>
       </c>
       <c r="B30" s="23">
-        <f>IF(A30&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A30&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C30" s="23">
@@ -2667,7 +2792,7 @@
         <v/>
       </c>
       <c r="D30" s="23">
-        <f>(E29+B30)*'Your Numbers'!$B$28</f>
+        <f>(E29+B30)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E30" s="24">
@@ -2680,7 +2805,7 @@
         <v>27</v>
       </c>
       <c r="B31" s="23">
-        <f>IF(A31&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A31&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C31" s="23">
@@ -2688,7 +2813,7 @@
         <v/>
       </c>
       <c r="D31" s="23">
-        <f>(E30+B31)*'Your Numbers'!$B$28</f>
+        <f>(E30+B31)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E31" s="24">
@@ -2701,7 +2826,7 @@
         <v>28</v>
       </c>
       <c r="B32" s="23">
-        <f>IF(A32&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A32&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C32" s="23">
@@ -2709,7 +2834,7 @@
         <v/>
       </c>
       <c r="D32" s="23">
-        <f>(E31+B32)*'Your Numbers'!$B$28</f>
+        <f>(E31+B32)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E32" s="24">
@@ -2722,7 +2847,7 @@
         <v>29</v>
       </c>
       <c r="B33" s="23">
-        <f>IF(A33&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A33&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C33" s="23">
@@ -2730,7 +2855,7 @@
         <v/>
       </c>
       <c r="D33" s="23">
-        <f>(E32+B33)*'Your Numbers'!$B$28</f>
+        <f>(E32+B33)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E33" s="24">
@@ -2743,7 +2868,7 @@
         <v>30</v>
       </c>
       <c r="B34" s="23">
-        <f>IF(A34&lt;='Your Numbers'!$B$29,'Your Numbers'!$B$27,0)</f>
+        <f>IF(A34&lt;='Your Numbers'!$B$33,'Your Numbers'!$B$31,0)</f>
         <v/>
       </c>
       <c r="C34" s="23">
@@ -2751,7 +2876,7 @@
         <v/>
       </c>
       <c r="D34" s="23">
-        <f>(E33+B34)*'Your Numbers'!$B$28</f>
+        <f>(E33+B34)*'Your Numbers'!$B$32</f>
         <v/>
       </c>
       <c r="E34" s="24">
